--- a/314e-ig/output/StructureDefinition-annotation-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-annotation-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T11:15:06+05:30</t>
+    <t>2026-05-13T15:29:14+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-annotation-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-annotation-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T15:29:14+05:30</t>
+    <t>2026-05-15T09:21:03+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-annotation-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-annotation-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T09:21:03+05:30</t>
+    <t>2026-05-16T07:30:07+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-annotation-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-annotation-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-16T07:30:07+05:30</t>
+    <t>2026-05-16T10:04:42+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-annotation-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-annotation-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-16T10:04:42+05:30</t>
+    <t>2026-05-16T10:41:11+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-annotation-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-annotation-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-16T10:41:11+05:30</t>
+    <t>2026-05-16T12:18:43+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-annotation-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-annotation-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-16T12:18:43+05:30</t>
+    <t>2026-05-16T12:58:39+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-annotation-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-annotation-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-16T12:58:39+05:30</t>
+    <t>2026-05-16T13:10:22+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-annotation-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-annotation-314e.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="130">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-16T13:10:22+05:30</t>
+    <t>2026-05-16T16:45:26+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -375,20 +375,36 @@
     <t>Organization is used when there's no need for specific attribution as to who made the comment.</t>
   </si>
   <si>
+    <t xml:space="preserve">type:$this}
+</t>
+  </si>
+  <si>
     <t>Act.participant[typeCode=AUT].role</t>
   </si>
   <si>
+    <t>Annotation.author[x]:authorReference</t>
+  </si>
+  <si>
+    <t>authorReference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Practitioner|Patient|RelatedPerson|Organization) {http://314e.com/fhir/StructureDefinition/reference-314e}
+</t>
+  </si>
+  <si>
     <t>Annotation.time</t>
   </si>
   <si>
-    <t xml:space="preserve">dateTime
+    <t xml:space="preserve">dateTime {http://314e.com/fhir/ig/StructureDefinition/datetime-314e}
 </t>
   </si>
   <si>
-    <t>When the annotation was made</t>
-  </si>
-  <si>
-    <t>Indicates when this particular annotation was made.</t>
+    <t>Annotation time in UTC with precision support</t>
+  </si>
+  <si>
+    <t>Date/time when the annotation was made.
+All timestamps SHALL be represented in UTC.
+Precision and approximation extensions may be used.</t>
   </si>
   <si>
     <t>Act.effectiveTime</t>
@@ -711,12 +727,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AL8"/>
+  <dimension ref="A1:AL9"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="28.1640625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="32.046875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="18.296875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="10.26953125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="14.49609375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="11.10546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.29296875" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.21484375" customWidth="true" bestFit="true"/>
@@ -724,7 +740,7 @@
     <col min="8" max="8" width="13.1171875" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="10.75390625" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="69.7890625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="98.0859375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1374,16 +1390,14 @@
         <v>20</v>
       </c>
       <c r="AB6" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="AC6" s="2"/>
       <c r="AD6" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>20</v>
+        <v>101</v>
       </c>
       <c r="AF6" t="s" s="2">
         <v>109</v>
@@ -1404,17 +1418,19 @@
         <v>84</v>
       </c>
       <c r="AL6" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="C7" s="2"/>
+        <v>109</v>
+      </c>
+      <c r="C7" t="s" s="2">
+        <v>118</v>
+      </c>
       <c r="D7" t="s" s="2">
         <v>20</v>
       </c>
@@ -1435,15 +1451,17 @@
         <v>110</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="N7" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N7" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
         <v>20</v>
@@ -1492,7 +1510,7 @@
         <v>20</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>76</v>
@@ -1510,15 +1528,15 @@
         <v>84</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1526,7 +1544,7 @@
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="G8" t="s" s="2">
         <v>87</v>
@@ -1541,13 +1559,13 @@
         <v>110</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="L8" t="s" s="2">
         <v>122</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="M8" t="s" s="2">
         <v>123</v>
-      </c>
-      <c r="M8" t="s" s="2">
-        <v>124</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1598,10 +1616,10 @@
         <v>20</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="AH8" t="s" s="2">
         <v>87</v>
@@ -1616,7 +1634,113 @@
         <v>84</v>
       </c>
       <c r="AL8" t="s" s="2">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
         <v>125</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E9" s="2"/>
+      <c r="F9" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G9" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H9" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I9" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J9" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="K9" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="L9" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="M9" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="N9" s="2"/>
+      <c r="O9" s="2"/>
+      <c r="P9" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q9" s="2"/>
+      <c r="R9" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S9" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T9" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U9" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V9" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W9" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X9" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y9" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z9" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA9" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB9" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC9" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD9" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE9" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF9" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="AG9" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH9" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI9" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ9" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AK9" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL9" t="s" s="2">
+        <v>129</v>
       </c>
     </row>
   </sheetData>

--- a/314e-ig/output/StructureDefinition-annotation-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-annotation-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-16T16:45:26+05:30</t>
+    <t>2026-05-17T00:25:02+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-annotation-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-annotation-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-17T00:25:02+05:30</t>
+    <t>2026-05-19T06:46:39+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-annotation-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-annotation-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-19T06:46:39+05:30</t>
+    <t>2026-05-19T11:54:54+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-annotation-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-annotation-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-19T11:54:54+05:30</t>
+    <t>2026-05-25T12:07:44+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-annotation-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-annotation-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T12:07:44+05:30</t>
+    <t>2026-05-25T12:34:12+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-annotation-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-annotation-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T12:34:12+05:30</t>
+    <t>2026-05-25T13:52:53+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-annotation-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-annotation-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T13:52:53+05:30</t>
+    <t>2026-05-25T14:14:21+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-annotation-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-annotation-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T14:14:21+05:30</t>
+    <t>2026-05-25T14:26:28+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-annotation-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-annotation-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T14:26:28+05:30</t>
+    <t>2026-05-25T14:41:34+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-annotation-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-annotation-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T14:41:34+05:30</t>
+    <t>2026-05-25T15:12:42+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-annotation-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-annotation-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T15:12:42+05:30</t>
+    <t>2026-05-25T15:24:41+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-annotation-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-annotation-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T15:24:41+05:30</t>
+    <t>2026-05-25T15:48:57+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-annotation-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-annotation-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T15:48:57+05:30</t>
+    <t>2026-05-25T16:36:06+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-annotation-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-annotation-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T16:36:06+05:30</t>
+    <t>2026-05-26T08:48:22+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-annotation-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-annotation-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T08:48:22+05:30</t>
+    <t>2026-05-26T12:06:33+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-annotation-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-annotation-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T12:06:33+05:30</t>
+    <t>2026-05-26T19:54:55+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-annotation-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-annotation-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T19:54:55+05:30</t>
+    <t>2026-06-10T16:33:40+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-annotation-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-annotation-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T16:33:40+05:30</t>
+    <t>2026-06-11T14:17:09+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-annotation-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-annotation-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T14:17:09+05:30</t>
+    <t>2026-06-18T13:36:33+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-annotation-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-annotation-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T13:36:33+05:30</t>
+    <t>2026-06-18T14:15:04+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-annotation-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-annotation-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T14:15:04+05:30</t>
+    <t>2026-06-18T16:14:31+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-annotation-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-annotation-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T16:14:31+05:30</t>
+    <t>2026-06-24T16:34:23+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-annotation-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-annotation-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T16:34:23+05:30</t>
+    <t>2026-06-29T17:18:47+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -388,7 +388,7 @@
     <t>authorReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|Patient|RelatedPerson|Organization) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/practitioner-314e|http://314e.com/fhir/StructureDefinition/patient-314e|http://314e.com/fhir/StructureDefinition/relatedperson-314e|http://314e.com/fhir/StructureDefinition/organization-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -740,7 +740,7 @@
     <col min="8" max="8" width="13.1171875" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="10.75390625" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="98.0859375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="251.296875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/314e-ig/output/StructureDefinition-annotation-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-annotation-314e.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="135">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T17:18:47+05:30</t>
+    <t>2026-07-01T18:18:44+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -354,6 +354,22 @@
   </si>
   <si>
     <t>Provides attachment-backed annotation or note content.</t>
+  </si>
+  <si>
+    <t>Annotation.extension:type</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://314e.com/fhir/StructureDefinition/annotationType-314e}
+</t>
+  </si>
+  <si>
+    <t>The type of annotation</t>
+  </si>
+  <si>
+    <t>The type of annotation. This extension can be used to map the v2 NTE-4 comment type field.</t>
   </si>
   <si>
     <t>Annotation.author[x]</t>
@@ -727,7 +743,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AL9"/>
+  <dimension ref="A1:AL10"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="32.046875" customWidth="true" bestFit="true"/>
@@ -1320,9 +1336,11 @@
         <v>109</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="C6" s="2"/>
+        <v>93</v>
+      </c>
+      <c r="C6" t="s" s="2">
+        <v>110</v>
+      </c>
       <c r="D6" t="s" s="2">
         <v>20</v>
       </c>
@@ -1340,7 +1358,7 @@
         <v>20</v>
       </c>
       <c r="J6" t="s" s="2">
-        <v>110</v>
+        <v>20</v>
       </c>
       <c r="K6" t="s" s="2">
         <v>111</v>
@@ -1351,9 +1369,7 @@
       <c r="M6" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="N6" t="s" s="2">
-        <v>114</v>
-      </c>
+      <c r="N6" s="2"/>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
         <v>20</v>
@@ -1390,47 +1406,47 @@
         <v>20</v>
       </c>
       <c r="AB6" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="AC6" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="AD6" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>101</v>
+        <v>20</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>83</v>
+        <v>103</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="AL6" t="s" s="2">
-        <v>116</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="C7" t="s" s="2">
-        <v>118</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
         <v>20</v>
       </c>
@@ -1448,19 +1464,19 @@
         <v>20</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="L7" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="M7" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="N7" t="s" s="2">
         <v>119</v>
-      </c>
-      <c r="L7" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="M7" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N7" t="s" s="2">
-        <v>114</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -1498,19 +1514,17 @@
         <v>20</v>
       </c>
       <c r="AB7" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC7" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="AC7" s="2"/>
       <c r="AD7" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE7" t="s" s="2">
-        <v>20</v>
+        <v>101</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>76</v>
@@ -1528,17 +1542,19 @@
         <v>84</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>116</v>
+        <v>121</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="C8" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="C8" t="s" s="2">
+        <v>123</v>
+      </c>
       <c r="D8" t="s" s="2">
         <v>20</v>
       </c>
@@ -1556,18 +1572,20 @@
         <v>20</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="N8" s="2"/>
+        <v>118</v>
+      </c>
+      <c r="N8" t="s" s="2">
+        <v>119</v>
+      </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
         <v>20</v>
@@ -1616,7 +1634,7 @@
         <v>20</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>76</v>
@@ -1634,7 +1652,7 @@
         <v>84</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="9">
@@ -1650,7 +1668,7 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="G9" t="s" s="2">
         <v>87</v>
@@ -1662,7 +1680,7 @@
         <v>20</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="K9" t="s" s="2">
         <v>126</v>
@@ -1725,7 +1743,7 @@
         <v>125</v>
       </c>
       <c r="AG9" t="s" s="2">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="AH9" t="s" s="2">
         <v>87</v>
@@ -1741,6 +1759,112 @@
       </c>
       <c r="AL9" t="s" s="2">
         <v>129</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E10" s="2"/>
+      <c r="F10" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G10" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H10" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I10" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J10" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="K10" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L10" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="M10" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
+      <c r="P10" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q10" s="2"/>
+      <c r="R10" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S10" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T10" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U10" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V10" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W10" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X10" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y10" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z10" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA10" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB10" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC10" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD10" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE10" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF10" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="AG10" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH10" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI10" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ10" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AK10" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL10" t="s" s="2">
+        <v>134</v>
       </c>
     </row>
   </sheetData>
